--- a/Assets/Document/云熹约定项目文档/11.配音文本/周杉配音文本.xlsx
+++ b/Assets/Document/云熹约定项目文档/11.配音文本/周杉配音文本.xlsx
@@ -29,10 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
-  <si>
-    <t>角色分析： 在校大学生，兼职陪玩。性格坚韧、情绪稳定，有着超出年龄的成熟和克制力。声音底色是干净的少年感，但在长期疲惫下会带一丝沙哑。他的“完美服务”是一种自我保护的外壳，偶尔泄露的真实情绪才是关键。</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="83">
   <si>
     <t>848字</t>
   </si>
@@ -46,21 +43,18 @@
     <t>“老板晚上好，我是时安。接下来的时间，我会全力配合您的节奏。”</t>
   </si>
   <si>
-    <t>极其温润、干净，顺着电流传来，语速适中，带着专业服务的温和</t>
+    <t>温润、干净，顺着电流传来，语速适中，带着专业服务的温和</t>
   </si>
   <si>
     <t>“左侧草丛安全，对方打野在下半区露头了，老板，您可以直接进场，我留了控制技能掩护你。”</t>
   </si>
   <si>
-    <t>温和但精准，语速平稳，不带多余情绪。每一个报点都清晰利落</t>
+    <t>温和但精准，语速平稳，不带多余情绪</t>
   </si>
   <si>
     <t>“我的错，刚才给你的护盾慢了，没保住你。”</t>
   </si>
   <si>
-    <t>极其平稳，没有叹气，没有情绪波动</t>
-  </si>
-  <si>
     <t>“对面双C为了抓你，已经交了全部关键技能和闪现。老板别急，我去清线守高地，你复活后直接带线拿龙，这局能翻，信我。”</t>
   </si>
   <si>
@@ -88,13 +82,13 @@
     <t>“老板晚上好，今天是想玩游戏，还是想随便聊聊天？”</t>
   </si>
   <si>
-    <t>带着淡淡倦意的青年音，有一点沙哑和慵懒，像是本来准备下线了却被消息拉了回来，语气比平时更松弛一些。</t>
+    <t>带着淡淡倦意，有一点沙哑和慵懒，语气比平时更松弛一些。</t>
   </si>
   <si>
     <t>“老板，你那边的背景音……你在医院？”</t>
   </si>
   <si>
-    <t>先有短暂的沉默（约三四秒，他在辨认声音），然后说出这句话。语速比平时慢了半拍，尾音泄露出一丝不易察觉的紧绷和担心。</t>
+    <t>先有短暂的沉默，然后说出这句话。语速比平时慢了半拍，尾音泄露出一丝不易察觉的紧绷和担心。</t>
   </si>
   <si>
     <t>“既然在输液，就别盯着手机屏幕看了，伤神。”</t>
@@ -112,13 +106,13 @@
     <t>“……拿钱办事是应该的，老板不用算得这么清楚。既然输完液了，就早点回去休息吧。”</t>
   </si>
   <si>
-    <t>先是轻轻地吸了一口气（很轻，但能捕捉到），然后说出这句话。语气里有一丝极淡的、不易察觉的遗憾，但没有推辞，保持着体面的克制。</t>
+    <t>先是轻轻地吸了一口气，然后说出这句话。语气里有一丝极淡的、不易察觉的遗憾，但没有推辞，保持着体面的克制。</t>
   </si>
   <si>
     <t>“能起作用就好……那我就不打扰老板休息了。回去的路上注意安全，如果可以的话，到家给我发个消息，好吗？”</t>
   </si>
   <si>
-    <t>前半句温和释然，后半句逐渐放轻。“好吗”二字说得极轻极柔，像是在问一个很重要的问题，又像是在给自己留一条退路。</t>
+    <t>前半句温和释然，后半句逐渐放轻。“好吗”二字说得极轻极柔</t>
   </si>
   <si>
     <t>“我……只是有点放心不下。”</t>
@@ -136,7 +130,7 @@
     <t>“呼……老板，下午好。抱歉，刚才风有点大，今天想聊点什么？”</t>
   </si>
   <si>
-    <t>先是沉重急促的喘息，夹杂风声和滚轮声。语速比平时快，尾音带着显而易见的沙哑和虚浮。他在极力调整呼吸，试图把疲惫感强压下去。</t>
+    <t>先是沉重急促的喘息，语速比平时快，尾音带着显而易见的沙哑和虚浮，试图把疲惫感强压下去。</t>
   </si>
   <si>
     <t>“嗯，接了个同城搬运的兼职。不影响的，老板可以说说你那边的风景，我听着呢。”</t>
@@ -160,7 +154,7 @@
     <t>“……可以不挂吗？就十分钟。我可以把钱退给你……我只是，现在真的很想再听听你的声音。”</t>
   </si>
   <si>
-    <t>声音带着生怕被拒绝的小心翼翼，甚至透出一丝哀求。语速变慢，每一个字都像是从喉咙里挤出来的。</t>
+    <t>声音带着生怕被拒绝的小心翼翼，甚至透出一丝哀求，语速变慢</t>
   </si>
   <si>
     <t>“老板你不用给我结算。”</t>
@@ -178,7 +172,7 @@
     <t>“啊？”</t>
   </si>
   <si>
-    <t>短促，带着一点意外和懵，像是没想到她会问这个问题。</t>
+    <t>短促，带着一点意外和懵</t>
   </si>
   <si>
     <t>“最近在看《被讨厌的勇气》，里面有一句话我记了很久——‘重要的不是被给予了什么，而是如何去利用被给予的东西’。”</t>
@@ -220,9 +214,6 @@
     <t>“好。”</t>
   </si>
   <si>
-    <t>很轻很轻地回应</t>
-  </si>
-  <si>
     <t>“其实……这段时间我一直在想，网络那端那个冷静又清醒的你，在现实中到底是个什么样的人。”</t>
   </si>
   <si>
@@ -268,7 +259,7 @@
     <t>“但是，我想试着跨出那条边界。我想成为你在这个世界上，可以偶尔卸下防备的、能随时依靠的底牌。”</t>
   </si>
   <si>
-    <t>语速更慢，“但是”之后有短暂停顿，像是给自己鼓足勇气。语气坚定而温柔，带着一种想要成为她支撑的恳切。</t>
+    <t>语速更慢，“但是”之后有短暂停顿，像是给自己鼓足勇气，语气坚定而温柔</t>
   </si>
   <si>
     <t>“对不起，是我冒昧了。既然是你的决定，我接受。能以朋友的身份陪着你，我已经很知足了。”</t>
@@ -299,17 +290,10 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="20"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -474,18 +458,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -858,52 +836,55 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
@@ -918,105 +899,105 @@
     <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1338,362 +1319,361 @@
     <col min="3" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="102" spans="1:2">
-      <c r="A1" s="2" t="s">
+    <row r="1" ht="25.5" spans="1:2">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+    </row>
+    <row r="2" ht="14.25" spans="1:2">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+    </row>
+    <row r="3" ht="26.25" spans="1:2">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="B2" s="4"/>
-    </row>
-    <row r="3" ht="26.25" spans="1:2">
-      <c r="A3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+    </row>
+    <row r="4" ht="18.75" spans="1:2">
+      <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" ht="18.75" spans="1:2">
-      <c r="A4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="6" t="s">
+    </row>
+    <row r="5" ht="18.75" spans="1:2">
+      <c r="A5" s="6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" ht="18.75" spans="1:2">
-      <c r="A5" s="7" t="s">
+      <c r="B5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="7" t="s">
+    </row>
+    <row r="6" ht="18.75" spans="1:2">
+      <c r="A6" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" ht="18.75" spans="1:2">
-      <c r="A6" s="7" t="s">
+      <c r="B6" s="7"/>
+    </row>
+    <row r="7" ht="37.5" spans="1:2">
+      <c r="A7" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" ht="37.5" spans="1:2">
-      <c r="A7" s="7" t="s">
+    <row r="8" ht="18.75" spans="1:2">
+      <c r="A8" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" ht="18.75" spans="1:2">
-      <c r="A8" s="7" t="s">
+    <row r="9" ht="18.75" spans="1:2">
+      <c r="A9" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" ht="18.75" spans="1:2">
-      <c r="A9" s="7" t="s">
+    <row r="10" ht="18.75" spans="1:2">
+      <c r="A10" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" ht="18.75" spans="1:2">
-      <c r="A10" s="7" t="s">
+    <row r="11" ht="18.75" spans="1:2">
+      <c r="A11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B11" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="11" ht="18.75" spans="1:2">
-      <c r="A11" s="7" t="s">
+    <row r="12" ht="18.75" spans="1:2">
+      <c r="A12" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B12" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="12" ht="37.5" spans="1:2">
-      <c r="A12" s="7" t="s">
+    <row r="13" ht="18.75" spans="1:2">
+      <c r="A13" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="13" ht="18.75" spans="1:2">
-      <c r="A13" s="7" t="s">
+    <row r="14" ht="18.75" spans="1:2">
+      <c r="A14" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B14" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="14" ht="18.75" spans="1:2">
-      <c r="A14" s="7" t="s">
+    <row r="15" ht="18.75" spans="1:2">
+      <c r="A15" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B15" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="15" ht="37.5" spans="1:2">
-      <c r="A15" s="7" t="s">
+    <row r="16" ht="37.5" spans="1:2">
+      <c r="A16" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B16" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="16" ht="37.5" spans="1:2">
-      <c r="A16" s="7" t="s">
+    <row r="17" ht="18.75" spans="1:2">
+      <c r="A17" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B17" s="6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="17" ht="18.75" spans="1:2">
-      <c r="A17" s="7" t="s">
+    <row r="18" ht="18.75" spans="1:2">
+      <c r="A18" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B18" s="6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="18" ht="18.75" spans="1:2">
-      <c r="A18" s="7" t="s">
+    <row r="19" ht="18.75" spans="1:2">
+      <c r="A19" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B19" s="6" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="19" ht="37.5" spans="1:2">
-      <c r="A19" s="7" t="s">
+    <row r="20" ht="18.75" spans="1:2">
+      <c r="A20" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B20" s="6" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="20" ht="18.75" spans="1:2">
-      <c r="A20" s="7" t="s">
+    <row r="21" ht="18.75" spans="1:2">
+      <c r="A21" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B21" s="6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="21" ht="18.75" spans="1:2">
-      <c r="A21" s="7" t="s">
+    <row r="22" ht="18.75" spans="1:2">
+      <c r="A22" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B22" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="22" ht="18.75" spans="1:2">
-      <c r="A22" s="7" t="s">
+    <row r="23" ht="18.75" spans="1:2">
+      <c r="A23" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B23" s="6" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="23" ht="18.75" spans="1:2">
-      <c r="A23" s="7" t="s">
+    <row r="24" ht="18.75" spans="1:2">
+      <c r="A24" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B24" s="6" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="24" ht="18.75" spans="1:2">
-      <c r="A24" s="7" t="s">
+    <row r="25" ht="18.75" spans="1:2">
+      <c r="A25" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B25" s="6" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="25" ht="18.75" spans="1:2">
-      <c r="A25" s="7" t="s">
+    <row r="26" ht="18.75" spans="1:2">
+      <c r="A26" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B26" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="26" ht="18.75" spans="1:2">
-      <c r="A26" s="7" t="s">
+    <row r="27" ht="37.5" spans="1:2">
+      <c r="A27" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B27" s="6" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="27" ht="37.5" spans="1:2">
-      <c r="A27" s="7" t="s">
+    <row r="28" ht="18.75" spans="1:2">
+      <c r="A28" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B28" s="6" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="28" ht="18.75" spans="1:2">
-      <c r="A28" s="7" t="s">
+    <row r="29" ht="18.75" spans="1:2">
+      <c r="A29" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B29" s="6" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="29" ht="18.75" spans="1:2">
-      <c r="A29" s="7" t="s">
+    <row r="30" ht="18.75" spans="1:2">
+      <c r="A30" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B30" s="6" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="30" ht="18.75" spans="1:2">
-      <c r="A30" s="7" t="s">
+    <row r="31" ht="18.75" spans="1:2">
+      <c r="A31" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B31" s="6" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="31" ht="18.75" spans="1:2">
-      <c r="A31" s="7" t="s">
+    <row r="32" ht="37.5" spans="1:2">
+      <c r="A32" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B32" s="8" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="32" ht="37.5" spans="1:2">
-      <c r="A32" s="7" t="s">
+    <row r="33" ht="18.75" spans="1:2">
+      <c r="A33" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B33" s="8"/>
+    </row>
+    <row r="34" ht="18.75" spans="1:2">
+      <c r="A34" s="6" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="33" ht="18.75" spans="1:2">
-      <c r="A33" s="7" t="s">
+      <c r="B34" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B33" s="7" t="s">
+    </row>
+    <row r="35" ht="18.75" spans="1:2">
+      <c r="A35" s="6" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="34" ht="18.75" spans="1:2">
-      <c r="A34" s="7" t="s">
+      <c r="B35" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B34" s="7" t="s">
+    </row>
+    <row r="36" ht="18.75" spans="1:2">
+      <c r="A36" s="6" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="35" ht="18.75" spans="1:2">
-      <c r="A35" s="7" t="s">
+      <c r="B36" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B35" s="7" t="s">
+    </row>
+    <row r="37" ht="18.75" spans="1:2">
+      <c r="A37" s="6" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="36" ht="18.75" spans="1:2">
-      <c r="A36" s="7" t="s">
+      <c r="B37" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B36" s="7" t="s">
+    </row>
+    <row r="38" ht="18.75" spans="1:2">
+      <c r="A38" s="6" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="37" ht="18.75" spans="1:2">
-      <c r="A37" s="7" t="s">
+      <c r="B38" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B37" s="7" t="s">
+    </row>
+    <row r="39" ht="18.75" spans="1:2">
+      <c r="A39" s="6" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="38" ht="18.75" spans="1:2">
-      <c r="A38" s="7" t="s">
+      <c r="B39" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B38" s="7" t="s">
+    </row>
+    <row r="40" ht="18.75" spans="1:2">
+      <c r="A40" s="6" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="39" ht="18.75" spans="1:2">
-      <c r="A39" s="7" t="s">
+      <c r="B40" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B39" s="7" t="s">
+    </row>
+    <row r="41" ht="37.5" spans="1:2">
+      <c r="A41" s="6" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="40" ht="18.75" spans="1:2">
-      <c r="A40" s="7" t="s">
+      <c r="B41" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B40" s="7" t="s">
+    </row>
+    <row r="42" ht="18.75" spans="1:2">
+      <c r="A42" s="6" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="41" ht="37.5" spans="1:2">
-      <c r="A41" s="7" t="s">
+      <c r="B42" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B41" s="7" t="s">
+    </row>
+    <row r="43" ht="18.75" spans="1:2">
+      <c r="A43" s="6" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="42" ht="18.75" spans="1:2">
-      <c r="A42" s="7" t="s">
+      <c r="B43" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B42" s="7" t="s">
+    </row>
+    <row r="44" ht="19.5" spans="1:2">
+      <c r="A44" s="9" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="43" ht="18.75" spans="1:2">
-      <c r="A43" s="7" t="s">
+      <c r="B44" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="B43" s="7" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="44" ht="19.5" spans="1:2">
-      <c r="A44" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="B44" s="8" t="s">
-        <v>85</v>
-      </c>
     </row>
     <row r="47" ht="18.75" spans="1:2">
-      <c r="A47" s="9"/>
-      <c r="B47" s="9"/>
+      <c r="A47" s="10"/>
+      <c r="B47" s="10"/>
     </row>
     <row r="48" ht="18.75" spans="1:2">
-      <c r="A48" s="9"/>
-      <c r="B48" s="9"/>
+      <c r="A48" s="10"/>
+      <c r="B48" s="10"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="B32:B33"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
